--- a/forecastingInSpreadsheets/solution/bakery_sales_solution.xlsx
+++ b/forecastingInSpreadsheets/solution/bakery_sales_solution.xlsx
@@ -329,6 +329,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -345,6 +346,7 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="YYYY-MM-DD" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -355,6 +357,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
